--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89022668</v>
+        <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101345</v>
+        <v>101582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1075,14 @@
           <t>(L.) Mill.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ö om Heden, väg W580, Dlr</t>
+          <t>Heden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1088,7 +1092,7 @@
         <v>6729431</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,17 +1116,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,21 +1132,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Leif Andersson, Rolf-Göran Carlsson</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1157,7 +1151,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89022668</t>
+          <t>https://artportalen.se/Sighting/136954304</t>
         </is>
       </c>
     </row>
@@ -1275,48 +1269,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4628544</v>
+        <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99781</v>
+        <v>99388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222309</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Heden, ost-sydost bystugan, Dlr</t>
+          <t>Lissheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499913</v>
+        <v>499777</v>
       </c>
       <c r="R7" t="n">
-        <v>6729284</v>
+        <v>6729313</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,17 +1342,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-06-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-06-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>enstaka exemplar finns även här och där på åsarna österut.</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,76 +1356,80 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Bryn mot sandig brukningsvägskant</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Dahlström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4628544</t>
+          <t>https://artportalen.se/Sighting/136954308</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89022696</v>
+        <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99781</v>
+        <v>99388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222309</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ö om Heden, väg W580, Dlr</t>
+          <t>Lissheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499815</v>
+        <v>499742</v>
       </c>
       <c r="R8" t="n">
-        <v>6729319</v>
+        <v>6729320</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,17 +1453,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,31 +1469,479 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954309</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4628544</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Heden, ost-sydost bystugan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499913</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6729284</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-06-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>enstaka exemplar finns även här och där på åsarna österut.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bryn mot sandig brukningsvägskant</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pär Dahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4628544</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>89022696</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99781</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ö om Heden, väg W580, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499815</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6729319</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Leif Andersson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Leif Andersson, Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89022696</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136954305</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100017</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backstarr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carex ericetorum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lissheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499811</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6729314</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954305</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136954307</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lissheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499827</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6729298</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954307</t>
         </is>
       </c>
     </row>
@@ -1510,6 +1954,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100017</v>
+        <v>100023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100023</v>
+        <v>100025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100025</v>
+        <v>100026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100026</v>
+        <v>100032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100032</v>
+        <v>100036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100036</v>
+        <v>100038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100038</v>
+        <v>100040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100040</v>
+        <v>100053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100053</v>
+        <v>100055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100055</v>
+        <v>100058</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100058</v>
+        <v>100068</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100068</v>
+        <v>100069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100069</v>
+        <v>100074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100074</v>
+        <v>100077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100077</v>
+        <v>100083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100083</v>
+        <v>100095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100095</v>
+        <v>100096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100096</v>
+        <v>100099</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100099</v>
+        <v>100100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 5005-2024 artfynd.xlsx
+++ b/artfynd/S 5005-2024 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>136954304</v>
       </c>
       <c r="B5" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>136954308</v>
       </c>
       <c r="B7" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>136954309</v>
       </c>
       <c r="B8" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>136954305</v>
       </c>
       <c r="B11" t="n">
-        <v>100100</v>
+        <v>100103</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>136954307</v>
       </c>
       <c r="B12" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
